--- a/data/trans_bre/P44-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P44-Provincia-trans_bre.xlsx
@@ -634,32 +634,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-6,01; 11,21</t>
+          <t>-5,7; 11,22</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-17,72; 4,06</t>
+          <t>-19,22; 4,32</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-39,44; -19,83</t>
+          <t>-38,47; -20,33</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-51,89; 283,28</t>
+          <t>-49,93; 265,68</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-61,76; 27,36</t>
+          <t>-63,65; 32,97</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-62,55; -38,8</t>
+          <t>-61,92; -39,92</t>
         </is>
       </c>
     </row>
@@ -714,32 +714,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-11,91; 2,59</t>
+          <t>-12,63; 2,14</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-6,71; 1,14</t>
+          <t>-6,72; 1,48</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-22,41; -7,27</t>
+          <t>-22,61; -7,47</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-63,12; 34,08</t>
+          <t>-65,16; 25,84</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-81,54; 64,38</t>
+          <t>-83,9; 65,97</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-60,46; -27,24</t>
+          <t>-60,61; -28,31</t>
         </is>
       </c>
     </row>
@@ -794,32 +794,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-7,0; 7,51</t>
+          <t>-7,37; 7,56</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-10,78; 5,68</t>
+          <t>-9,98; 6,12</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-10,09; 6,49</t>
+          <t>-10,7; 6,76</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-59,92; 167,44</t>
+          <t>-57,35; 179,36</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-57,99; 54,73</t>
+          <t>-55,76; 60,83</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-25,13; 21,1</t>
+          <t>-25,96; 22,18</t>
         </is>
       </c>
     </row>
@@ -874,32 +874,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-6,23; 8,08</t>
+          <t>-5,67; 7,78</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-12,61; 2,59</t>
+          <t>-12,98; 2,74</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-8,07; 8,19</t>
+          <t>-8,97; 7,92</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-53,22; 214,02</t>
+          <t>-51,84; 178,36</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-62,68; 24,28</t>
+          <t>-62,32; 26,73</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-22,46; 32,05</t>
+          <t>-24,62; 30,5</t>
         </is>
       </c>
     </row>
@@ -954,32 +954,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-8,81; 7,0</t>
+          <t>-9,43; 7,85</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-5,03; 5,33</t>
+          <t>-4,85; 5,59</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-11,63; 4,38</t>
+          <t>-11,64; 3,71</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-77,37; 185,52</t>
+          <t>-75,76; 262,56</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-85,73; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-51,06; 41,38</t>
+          <t>-49,83; 31,52</t>
         </is>
       </c>
     </row>
@@ -1034,32 +1034,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-11,29; 1,5</t>
+          <t>-12,09; 1,35</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-9,62; 4,94</t>
+          <t>-9,96; 3,69</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-13,26; 2,41</t>
+          <t>-13,21; 2,12</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-82,66; 38,02</t>
+          <t>-85,72; 40,25</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-74,92; 118,71</t>
+          <t>-76,17; 75,83</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-39,66; 9,61</t>
+          <t>-39,5; 8,35</t>
         </is>
       </c>
     </row>
@@ -1114,32 +1114,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-5,02; 5,33</t>
+          <t>-4,94; 4,97</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-11,65; 0,28</t>
+          <t>-11,75; -0,09</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-32,35; 3,77</t>
+          <t>-35,08; 2,9</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-48,99; 110,15</t>
+          <t>-48,88; 102,49</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-58,73; 7,59</t>
+          <t>-59,96; 4,03</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-79,6; 10,62</t>
+          <t>-81,19; 8,53</t>
         </is>
       </c>
     </row>
@@ -1194,32 +1194,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-11,34; -1,78</t>
+          <t>-11,33; -1,31</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-8,8; -1,0</t>
+          <t>-9,15; -1,12</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-53,47; -2,92</t>
+          <t>-52,66; -2,56</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-80,08; -20,9</t>
+          <t>-80,46; -17,48</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-78,4; -13,82</t>
+          <t>-79,33; -13,13</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-61,23; -7,23</t>
+          <t>-60,89; -6,61</t>
         </is>
       </c>
     </row>
@@ -1274,32 +1274,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-4,74; 0,09</t>
+          <t>-4,39; 0,09</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-6,76; -2,17</t>
+          <t>-6,49; -2,01</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-41,06; -8,19</t>
+          <t>-44,62; -7,68</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-41,63; 1,93</t>
+          <t>-40,43; 1,06</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-50,88; -19,52</t>
+          <t>-49,51; -18,48</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-66,99; -22,27</t>
+          <t>-70,53; -21,23</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P44-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P44-Provincia-trans_bre.xlsx
@@ -606,7 +606,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-29,17</t>
+          <t>-25,88</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -621,7 +621,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-51,51%</t>
+          <t>-48,73%</t>
         </is>
       </c>
     </row>
@@ -634,32 +634,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-5,7; 11,22</t>
+          <t>-6,02; 11,87</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-19,22; 4,32</t>
+          <t>-18,01; 3,69</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-38,47; -20,33</t>
+          <t>-33,89; -16,38</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-49,93; 265,68</t>
+          <t>-53,63; 282,05</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-63,65; 32,97</t>
+          <t>-64,51; 25,56</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-61,92; -39,92</t>
+          <t>-59,29; -34,9</t>
         </is>
       </c>
     </row>
@@ -686,7 +686,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-15,24</t>
+          <t>-14,6</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -701,7 +701,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-47,49%</t>
+          <t>-46,14%</t>
         </is>
       </c>
     </row>
@@ -714,32 +714,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-12,63; 2,14</t>
+          <t>-12,61; 1,85</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-6,72; 1,48</t>
+          <t>-6,45; 0,74</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-22,61; -7,47</t>
+          <t>-22,2; -7,65</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-65,16; 25,84</t>
+          <t>-65,88; 20,07</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-83,9; 65,97</t>
+          <t>-82,97; 42,78</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-60,61; -28,31</t>
+          <t>-60,45; -27,9</t>
         </is>
       </c>
     </row>
@@ -766,7 +766,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-2,34</t>
+          <t>-1,63</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -781,7 +781,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-6,49%</t>
+          <t>-4,54%</t>
         </is>
       </c>
     </row>
@@ -794,32 +794,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-7,37; 7,56</t>
+          <t>-6,73; 8,26</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-9,98; 6,12</t>
+          <t>-11,21; 5,52</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-10,7; 6,76</t>
+          <t>-10,91; 5,67</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-57,35; 179,36</t>
+          <t>-59,46; 203,8</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-55,76; 60,83</t>
+          <t>-59,69; 56,13</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-25,96; 22,18</t>
+          <t>-26,21; 17,75</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-0,31</t>
+          <t>-0,33</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-1,0%</t>
+          <t>-1,04%</t>
         </is>
       </c>
     </row>
@@ -874,32 +874,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-5,67; 7,78</t>
+          <t>-6,84; 7,64</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-12,98; 2,74</t>
+          <t>-13,35; 2,53</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-8,97; 7,92</t>
+          <t>-7,92; 7,64</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-51,84; 178,36</t>
+          <t>-56,4; 180,13</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-62,32; 26,73</t>
+          <t>-67,28; 22,31</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-24,62; 30,5</t>
+          <t>-22,4; 28,92</t>
         </is>
       </c>
     </row>
@@ -926,7 +926,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-3,33</t>
+          <t>-2,85</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -941,7 +941,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-19,78%</t>
+          <t>-17,32%</t>
         </is>
       </c>
     </row>
@@ -954,22 +954,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-9,43; 7,85</t>
+          <t>-9,69; 6,93</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-4,85; 5,59</t>
+          <t>-4,99; 5,35</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-11,64; 3,71</t>
+          <t>-10,44; 4,2</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-75,76; 262,56</t>
+          <t>-72,75; 254,37</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-49,83; 31,52</t>
+          <t>-49,21; 36,63</t>
         </is>
       </c>
     </row>
@@ -1006,7 +1006,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-5,52</t>
+          <t>-5,14</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-18,86%</t>
+          <t>-17,91%</t>
         </is>
       </c>
     </row>
@@ -1034,32 +1034,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-12,09; 1,35</t>
+          <t>-11,75; 0,96</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-9,96; 3,69</t>
+          <t>-10,32; 3,88</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-13,21; 2,12</t>
+          <t>-12,68; 2,73</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-85,72; 40,25</t>
+          <t>-83,89; 27,36</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-76,17; 75,83</t>
+          <t>-74,93; 82,8</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-39,5; 8,35</t>
+          <t>-38,67; 11,42</t>
         </is>
       </c>
     </row>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-14,22</t>
+          <t>0,74</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-38,48%</t>
+          <t>2,0%</t>
         </is>
       </c>
     </row>
@@ -1114,32 +1114,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-4,94; 4,97</t>
+          <t>-5,71; 5,18</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-11,75; -0,09</t>
+          <t>-11,39; 0,44</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-35,08; 2,9</t>
+          <t>-6,07; 7,11</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-48,88; 102,49</t>
+          <t>-53,06; 113,47</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-59,96; 4,03</t>
+          <t>-60,99; 4,23</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-81,19; 8,53</t>
+          <t>-14,49; 22,21</t>
         </is>
       </c>
     </row>
@@ -1166,7 +1166,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-30,43</t>
+          <t>-3,8</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-45,04%</t>
+          <t>-9,19%</t>
         </is>
       </c>
     </row>
@@ -1194,32 +1194,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-11,33; -1,31</t>
+          <t>-11,47; -1,63</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-9,15; -1,12</t>
+          <t>-8,91; -1,2</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-52,66; -2,56</t>
+          <t>-10,06; 2,86</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-80,46; -17,48</t>
+          <t>-78,86; -18,28</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-79,33; -13,13</t>
+          <t>-80,38; -13,73</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-60,89; -6,61</t>
+          <t>-22,35; 7,32</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>-19,13</t>
+          <t>-5,84</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1261,7 +1261,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-41,9%</t>
+          <t>-16,18%</t>
         </is>
       </c>
     </row>
@@ -1274,32 +1274,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-4,39; 0,09</t>
+          <t>-4,35; 0,19</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-6,49; -2,01</t>
+          <t>-6,55; -2,1</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-44,62; -7,68</t>
+          <t>-8,49; -3,0</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-40,43; 1,06</t>
+          <t>-39,97; 3,91</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-49,51; -18,48</t>
+          <t>-50,87; -19,48</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-70,53; -21,23</t>
+          <t>-22,73; -8,63</t>
         </is>
       </c>
     </row>
